--- a/artfynd/A 57417-2025 artfynd.xlsx
+++ b/artfynd/A 57417-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89600113</v>
+        <v>89600116</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387604.9963154738</v>
+        <v>387588</v>
       </c>
       <c r="R2" t="n">
-        <v>7029669.186588053</v>
+        <v>7029814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89600119</v>
+        <v>89600099</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387593.8934110273</v>
+        <v>387587</v>
       </c>
       <c r="R3" t="n">
-        <v>7029608.978810107</v>
+        <v>7029633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89600109</v>
+        <v>89600097</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387581.8892630802</v>
+        <v>387615</v>
       </c>
       <c r="R4" t="n">
-        <v>7029651.145281734</v>
+        <v>7029787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89600099</v>
+        <v>89600098</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387587.0957404382</v>
+        <v>387582</v>
       </c>
       <c r="R5" t="n">
-        <v>7029633.007700368</v>
+        <v>7029651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89600098</v>
+        <v>89600112</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387581.8892630802</v>
+        <v>387900</v>
       </c>
       <c r="R6" t="n">
-        <v>7029651.145281734</v>
+        <v>7029661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89600097</v>
+        <v>89600113</v>
       </c>
       <c r="B7" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387614.9704812302</v>
+        <v>387605</v>
       </c>
       <c r="R7" t="n">
-        <v>7029786.886122441</v>
+        <v>7029669</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89600114</v>
+        <v>89600109</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387616.1755853556</v>
+        <v>387582</v>
       </c>
       <c r="R8" t="n">
-        <v>7029782.804176963</v>
+        <v>7029651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57417-2025 artfynd.xlsx
+++ b/artfynd/A 57417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600116</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600098</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600112</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600113</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>